--- a/data/trans_camb/IP16B02-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16B02-Edad-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,16; 0,0</t>
+          <t>-16,3; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,22 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-25,75; 0,0</t>
+          <t>-25,66; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-25,42; 0,0</t>
+          <t>-23,29; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,26; -2,0</t>
+          <t>-14,71; -1,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 0,0</t>
+          <t>-13,13; 0,0</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,16; 0,0</t>
+          <t>-16,3; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -717,22 +717,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-25,75; 0,0</t>
+          <t>-25,66; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-25,42; 0,0</t>
+          <t>-23,29; 0,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,26; -2,0</t>
+          <t>-14,71; -1,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 0,0</t>
+          <t>-13,13; 0,0</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-22,68; 25,55</t>
+          <t>-23,0; 22,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-18,35; 29,2</t>
+          <t>-20,15; 24,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-30,11; -1,13</t>
+          <t>-30,99; -1,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 10,81</t>
+          <t>-8,56; 11,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-21,6; 2,97</t>
+          <t>-21,06; 4,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 11,01</t>
+          <t>-14,38; 10,23</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-26,38; 44,24</t>
+          <t>-26,31; 39,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-21,18; 52,82</t>
+          <t>-22,6; 42,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-30,8; -1,66</t>
+          <t>-32,91; -2,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 12,16</t>
+          <t>-8,77; 13,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,02; 3,49</t>
+          <t>-23,4; 4,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 13,84</t>
+          <t>-15,97; 12,55</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-41,52; -7,84</t>
+          <t>-42,17; -7,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-29,81; 0,0</t>
+          <t>-25,8; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-27,1; 0,0</t>
+          <t>-30,78; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-36,83; -4,03</t>
+          <t>-37,28; -4,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-28,43; -6,8</t>
+          <t>-27,84; -6,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,84; -4,76</t>
+          <t>-26,19; -4,66</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-41,52; -7,84</t>
+          <t>-42,17; -7,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-29,81; 0,0</t>
+          <t>-25,8; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-27,1; 0,0</t>
+          <t>-30,78; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-36,83; -4,03</t>
+          <t>-37,28; -4,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-28,43; -6,8</t>
+          <t>-27,84; -6,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-25,84; -4,76</t>
+          <t>-26,19; -4,66</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-25,27; 30,85</t>
+          <t>-26,19; 33,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-20,07; 36,17</t>
+          <t>-18,18; 38,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,22; 51,71</t>
+          <t>7,93; 51,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,87; 47,98</t>
+          <t>0,3; 48,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 33,64</t>
+          <t>-5,55; 34,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 33,46</t>
+          <t>-4,66; 33,56</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-31,86; 71,05</t>
+          <t>-32,56; 74,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-23,32; 81,69</t>
+          <t>-21,04; 92,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,36; 121,55</t>
+          <t>13,86; 121,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,58; 96,12</t>
+          <t>2,15; 106,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 64,53</t>
+          <t>-7,1; 68,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 64,17</t>
+          <t>-5,57; 65,67</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 13,85</t>
+          <t>-10,37; 14,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 15,17</t>
+          <t>-9,19; 15,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 8,45</t>
+          <t>-10,59; 8,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 11,43</t>
+          <t>-6,62; 11,3</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 6,78</t>
+          <t>-8,88; 6,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 9,32</t>
+          <t>-6,65; 8,3</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 19,7</t>
+          <t>-11,89; 21,32</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 21,35</t>
+          <t>-10,72; 21,07</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-11,59; 9,86</t>
+          <t>-11,32; 9,73</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 13,8</t>
+          <t>-7,05; 13,79</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 8,24</t>
+          <t>-9,8; 8,24</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 11,44</t>
+          <t>-7,56; 10,25</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B02-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16B02-Edad-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,3; 0,0</t>
+          <t>-18,26; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,22 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-25,66; 0,0</t>
+          <t>-23,08; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,29; 0,0</t>
+          <t>-29,84; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,71; -1,97</t>
+          <t>-13,76; -1,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 0,0</t>
+          <t>-15,37; 0,0</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,3; 0,0</t>
+          <t>-18,26; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -717,22 +717,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-25,66; 0,0</t>
+          <t>-23,08; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-23,29; 0,0</t>
+          <t>-29,84; 0,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,71; -1,97</t>
+          <t>-13,76; -1,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 0,0</t>
+          <t>-15,37; 0,0</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-23,0; 22,78</t>
+          <t>-20,48; 24,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,15; 24,46</t>
+          <t>-20,51; 25,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-30,99; -1,6</t>
+          <t>-30,2; -1,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 11,3</t>
+          <t>-8,53; 11,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-21,06; 4,33</t>
+          <t>-23,03; 3,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,38; 10,23</t>
+          <t>-13,53; 10,4</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-26,31; 39,36</t>
+          <t>-23,77; 42,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-22,6; 42,12</t>
+          <t>-22,99; 44,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-32,91; -2,33</t>
+          <t>-31,84; -1,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 13,04</t>
+          <t>-8,86; 13,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,4; 4,97</t>
+          <t>-25,13; 4,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,97; 12,55</t>
+          <t>-14,92; 13,42</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-42,17; -7,75</t>
+          <t>-39,44; -7,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-25,8; 0,0</t>
+          <t>-32,54; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-30,78; 0,0</t>
+          <t>-31,72; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-37,28; -4,68</t>
+          <t>-38,39; -4,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-27,84; -6,57</t>
+          <t>-29,98; -6,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-26,19; -4,66</t>
+          <t>-24,06; -4,14</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-42,17; -7,75</t>
+          <t>-39,44; -7,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-25,8; 0,0</t>
+          <t>-32,54; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-30,78; 0,0</t>
+          <t>-31,72; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-37,28; -4,68</t>
+          <t>-38,39; -4,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-27,84; -6,57</t>
+          <t>-29,98; -6,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-26,19; -4,66</t>
+          <t>-24,06; -4,14</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-26,19; 33,36</t>
+          <t>-23,8; 35,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-18,18; 38,84</t>
+          <t>-18,31; 36,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,93; 51,23</t>
+          <t>7,68; 52,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 48,96</t>
+          <t>2,05; 49,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 34,96</t>
+          <t>-3,59; 32,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 33,56</t>
+          <t>-5,34; 33,66</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-32,56; 74,21</t>
+          <t>-31,13; 84,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-21,04; 92,54</t>
+          <t>-22,62; 84,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,86; 121,66</t>
+          <t>9,97; 130,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,15; 106,97</t>
+          <t>2,78; 109,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 68,35</t>
+          <t>-4,51; 63,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 65,67</t>
+          <t>-5,97; 65,59</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 14,61</t>
+          <t>-10,93; 14,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 15,33</t>
+          <t>-9,26; 15,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 8,02</t>
+          <t>-9,97; 8,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 11,3</t>
+          <t>-7,17; 10,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 6,55</t>
+          <t>-8,29; 5,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 8,3</t>
+          <t>-5,57; 8,88</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 21,32</t>
+          <t>-12,71; 19,88</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 21,07</t>
+          <t>-10,58; 22,07</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 9,73</t>
+          <t>-10,94; 9,68</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 13,79</t>
+          <t>-7,7; 13,1</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 8,24</t>
+          <t>-9,23; 7,29</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 10,25</t>
+          <t>-6,24; 10,92</t>
         </is>
       </c>
     </row>
